--- a/data/ams_weekly_data/Audio_Array/ads_report_week32.xlsx
+++ b/data/ams_weekly_data/Audio_Array/ads_report_week32.xlsx
@@ -1,14 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SP" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="SP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="SD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="SB" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +19,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +36,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +44,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,42 +419,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
@@ -493,10 +482,10 @@
         <v>18206</v>
       </c>
       <c r="G2" t="n">
-        <v>3088.98</v>
+        <v>6177.96</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -549,10 +538,10 @@
         <v>22501</v>
       </c>
       <c r="G4" t="n">
-        <v>16717.78</v>
+        <v>17886.42</v>
       </c>
       <c r="H4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
@@ -633,7 +622,7 @@
         <v>12202</v>
       </c>
       <c r="G7" t="n">
-        <v>10572</v>
+        <v>10682.17</v>
       </c>
       <c r="H7" t="n">
         <v>8</v>
@@ -661,10 +650,10 @@
         <v>123739</v>
       </c>
       <c r="G8" t="n">
-        <v>39379.69</v>
+        <v>41614.44</v>
       </c>
       <c r="H8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
@@ -857,7 +846,7 @@
         <v>96780</v>
       </c>
       <c r="G15" t="n">
-        <v>37848.33</v>
+        <v>37965.28</v>
       </c>
       <c r="H15" t="n">
         <v>15</v>
@@ -910,13 +899,13 @@
         <v>1143</v>
       </c>
       <c r="F17" t="n">
-        <v>68252</v>
+        <v>68250</v>
       </c>
       <c r="G17" t="n">
-        <v>65477.99</v>
+        <v>67595.78999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18">
@@ -1025,10 +1014,10 @@
         <v>15568</v>
       </c>
       <c r="G21" t="n">
-        <v>12947.46</v>
+        <v>14141.53</v>
       </c>
       <c r="H21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22">
@@ -1162,10 +1151,10 @@
         <v>523</v>
       </c>
       <c r="F26" t="n">
-        <v>49277</v>
+        <v>49275</v>
       </c>
       <c r="G26" t="n">
-        <v>59171.16</v>
+        <v>59679.64</v>
       </c>
       <c r="H26" t="n">
         <v>15</v>
@@ -1358,7 +1347,7 @@
         <v>97</v>
       </c>
       <c r="F33" t="n">
-        <v>9907</v>
+        <v>9906</v>
       </c>
       <c r="G33" t="n">
         <v>2003.39</v>
@@ -1501,10 +1490,10 @@
         <v>50003</v>
       </c>
       <c r="G38" t="n">
-        <v>51817.75999999999</v>
+        <v>56003.35000000001</v>
       </c>
       <c r="H38" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="39">
@@ -1613,10 +1602,10 @@
         <v>220812</v>
       </c>
       <c r="G42" t="n">
-        <v>67105.92</v>
+        <v>58212.7</v>
       </c>
       <c r="H42" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43">
@@ -1644,7 +1633,7 @@
         <v>28855.07</v>
       </c>
       <c r="H43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44">
@@ -1666,7 +1655,7 @@
         <v>476</v>
       </c>
       <c r="F44" t="n">
-        <v>92436</v>
+        <v>92434</v>
       </c>
       <c r="G44" t="n">
         <v>10050.84</v>
@@ -1750,7 +1739,7 @@
         <v>316</v>
       </c>
       <c r="F47" t="n">
-        <v>40454</v>
+        <v>40453</v>
       </c>
       <c r="G47" t="n">
         <v>21290.71</v>
@@ -1778,13 +1767,13 @@
         <v>771</v>
       </c>
       <c r="F48" t="n">
-        <v>75946</v>
+        <v>75942</v>
       </c>
       <c r="G48" t="n">
-        <v>37352.6</v>
+        <v>35871.24</v>
       </c>
       <c r="H48" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="49">
@@ -1921,10 +1910,10 @@
         <v>163033</v>
       </c>
       <c r="G53" t="n">
-        <v>185775.45</v>
+        <v>187809.35</v>
       </c>
       <c r="H53" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="54">
@@ -1949,10 +1938,10 @@
         <v>39093</v>
       </c>
       <c r="G54" t="n">
-        <v>59527.14</v>
+        <v>55969.50999999999</v>
       </c>
       <c r="H54" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="55">
@@ -2422,7 +2411,7 @@
         <v>38</v>
       </c>
       <c r="F71" t="n">
-        <v>9060</v>
+        <v>9059</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2506,7 +2495,7 @@
         <v>188</v>
       </c>
       <c r="F74" t="n">
-        <v>46643</v>
+        <v>46613</v>
       </c>
       <c r="G74" t="n">
         <v>9794.07</v>
@@ -2761,10 +2750,10 @@
         <v>13572</v>
       </c>
       <c r="G83" t="n">
-        <v>1355.08</v>
+        <v>2625.42</v>
       </c>
       <c r="H83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
@@ -2901,10 +2890,10 @@
         <v>14084</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>1283.9</v>
       </c>
       <c r="H88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
@@ -2954,7 +2943,7 @@
         <v>229</v>
       </c>
       <c r="F90" t="n">
-        <v>46925</v>
+        <v>46909</v>
       </c>
       <c r="G90" t="n">
         <v>9398.290000000001</v>
@@ -3013,10 +3002,10 @@
         <v>88266</v>
       </c>
       <c r="G92" t="n">
-        <v>3994.91</v>
+        <v>6991.52</v>
       </c>
       <c r="H92" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="93">
@@ -3038,7 +3027,7 @@
         <v>1570</v>
       </c>
       <c r="F93" t="n">
-        <v>191089</v>
+        <v>191088</v>
       </c>
       <c r="G93" t="n">
         <v>17379.69</v>
@@ -3066,7 +3055,7 @@
         <v>40</v>
       </c>
       <c r="F94" t="n">
-        <v>16142</v>
+        <v>16141</v>
       </c>
       <c r="G94" t="n">
         <v>3930.51</v>
@@ -3318,13 +3307,13 @@
         <v>496</v>
       </c>
       <c r="F103" t="n">
-        <v>52676</v>
+        <v>52675</v>
       </c>
       <c r="G103" t="n">
-        <v>9717.83</v>
+        <v>10132.24</v>
       </c>
       <c r="H103" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="104">
@@ -3374,13 +3363,13 @@
         <v>2448</v>
       </c>
       <c r="F105" t="n">
-        <v>457034</v>
+        <v>457023</v>
       </c>
       <c r="G105" t="n">
-        <v>28357.6</v>
+        <v>29526.24</v>
       </c>
       <c r="H105" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="106">
@@ -3402,7 +3391,7 @@
         <v>680</v>
       </c>
       <c r="F106" t="n">
-        <v>110320</v>
+        <v>110318</v>
       </c>
       <c r="G106" t="n">
         <v>15297.47</v>
@@ -3430,7 +3419,7 @@
         <v>154</v>
       </c>
       <c r="F107" t="n">
-        <v>33208</v>
+        <v>33207</v>
       </c>
       <c r="G107" t="n">
         <v>9009.310000000001</v>
@@ -3766,7 +3755,7 @@
         <v>224</v>
       </c>
       <c r="F119" t="n">
-        <v>21158</v>
+        <v>21157</v>
       </c>
       <c r="G119" t="n">
         <v>10464.41</v>
@@ -3794,7 +3783,7 @@
         <v>137</v>
       </c>
       <c r="F120" t="n">
-        <v>21806</v>
+        <v>21804</v>
       </c>
       <c r="G120" t="n">
         <v>7031.349999999999</v>
@@ -3909,10 +3898,10 @@
         <v>22961</v>
       </c>
       <c r="G124" t="n">
-        <v>6097.469999999999</v>
+        <v>3810.18</v>
       </c>
       <c r="H124" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="125">
@@ -4021,10 +4010,10 @@
         <v>169517</v>
       </c>
       <c r="G128" t="n">
-        <v>20419.49</v>
+        <v>22020.34</v>
       </c>
       <c r="H128" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="129">
@@ -4105,10 +4094,10 @@
         <v>60135</v>
       </c>
       <c r="G131" t="n">
-        <v>25009.29</v>
+        <v>28745.73</v>
       </c>
       <c r="H131" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="132">
@@ -4298,7 +4287,7 @@
         <v>940</v>
       </c>
       <c r="F138" t="n">
-        <v>26377</v>
+        <v>26376</v>
       </c>
       <c r="G138" t="n">
         <v>75424.19</v>
@@ -4357,10 +4346,10 @@
         <v>42477</v>
       </c>
       <c r="G140" t="n">
-        <v>55038.99000000001</v>
+        <v>41159.33</v>
       </c>
       <c r="H140" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="141">
@@ -4413,10 +4402,10 @@
         <v>30961</v>
       </c>
       <c r="G142" t="n">
-        <v>22527.12</v>
+        <v>24644.92</v>
       </c>
       <c r="H142" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="143">
@@ -4777,10 +4766,10 @@
         <v>20457</v>
       </c>
       <c r="G155" t="n">
-        <v>41714.4</v>
+        <v>45450.84</v>
       </c>
       <c r="H155" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="156">
@@ -4830,7 +4819,7 @@
         <v>250</v>
       </c>
       <c r="F157" t="n">
-        <v>83146</v>
+        <v>83145</v>
       </c>
       <c r="G157" t="n">
         <v>13047.44</v>
@@ -4861,10 +4850,10 @@
         <v>30974</v>
       </c>
       <c r="G158" t="n">
-        <v>9196.6</v>
+        <v>6350.84</v>
       </c>
       <c r="H158" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="159">
@@ -5194,13 +5183,13 @@
         <v>204</v>
       </c>
       <c r="F170" t="n">
-        <v>23075</v>
+        <v>23074</v>
       </c>
       <c r="G170" t="n">
-        <v>14283.87</v>
+        <v>16621.15</v>
       </c>
       <c r="H170" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="171">
@@ -5216,19 +5205,19 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>5134.09</v>
+        <v>5113.190000000001</v>
       </c>
       <c r="E171" t="n">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F171" t="n">
-        <v>45980</v>
+        <v>45977</v>
       </c>
       <c r="G171" t="n">
-        <v>12103.37</v>
+        <v>10934.73</v>
       </c>
       <c r="H171" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="172">
@@ -5449,10 +5438,10 @@
         <v>25307</v>
       </c>
       <c r="G179" t="n">
-        <v>4744.06</v>
+        <v>6978.809999999999</v>
       </c>
       <c r="H179" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="180">
@@ -5614,7 +5603,7 @@
         <v>509</v>
       </c>
       <c r="F185" t="n">
-        <v>55341</v>
+        <v>55339</v>
       </c>
       <c r="G185" t="n">
         <v>23877.98</v>
@@ -5670,7 +5659,7 @@
         <v>566</v>
       </c>
       <c r="F187" t="n">
-        <v>94040</v>
+        <v>94039</v>
       </c>
       <c r="G187" t="n">
         <v>12311.87</v>
@@ -5701,10 +5690,10 @@
         <v>47666</v>
       </c>
       <c r="G188" t="n">
-        <v>16774.57</v>
+        <v>19009.32</v>
       </c>
       <c r="H188" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="189">
@@ -5838,7 +5827,7 @@
         <v>100</v>
       </c>
       <c r="F193" t="n">
-        <v>113755</v>
+        <v>113754</v>
       </c>
       <c r="G193" t="n">
         <v>4575.42</v>
@@ -5953,10 +5942,10 @@
         <v>9691</v>
       </c>
       <c r="G197" t="n">
-        <v>7866.940000000001</v>
+        <v>10328.8</v>
       </c>
       <c r="H197" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="198">
@@ -6065,10 +6054,10 @@
         <v>15709</v>
       </c>
       <c r="G201" t="n">
-        <v>5039.820000000001</v>
+        <v>5908.46</v>
       </c>
       <c r="H201" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="202">
@@ -6084,13 +6073,13 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>1411.05</v>
+        <v>1394.61</v>
       </c>
       <c r="E202" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F202" t="n">
-        <v>12274</v>
+        <v>12273</v>
       </c>
       <c r="G202" t="n">
         <v>4592.36</v>
@@ -6118,7 +6107,7 @@
         <v>119</v>
       </c>
       <c r="F203" t="n">
-        <v>19851</v>
+        <v>19850</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -6146,13 +6135,13 @@
         <v>338</v>
       </c>
       <c r="F204" t="n">
-        <v>73047</v>
+        <v>73043</v>
       </c>
       <c r="G204" t="n">
-        <v>4955.08</v>
+        <v>6149.15</v>
       </c>
       <c r="H204" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="205">
@@ -6180,7 +6169,7 @@
         <v>3388.14</v>
       </c>
       <c r="H205" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="206">
@@ -6454,7 +6443,7 @@
         <v>405</v>
       </c>
       <c r="F215" t="n">
-        <v>111209</v>
+        <v>111205</v>
       </c>
       <c r="G215" t="n">
         <v>3133.9</v>
@@ -6566,7 +6555,7 @@
         <v>304</v>
       </c>
       <c r="F219" t="n">
-        <v>33793</v>
+        <v>33792</v>
       </c>
       <c r="G219" t="n">
         <v>12705.08</v>
@@ -6737,10 +6726,10 @@
         <v>155181</v>
       </c>
       <c r="G225" t="n">
-        <v>83874.60000000001</v>
+        <v>90228</v>
       </c>
       <c r="H225" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="226">
@@ -6762,7 +6751,7 @@
         <v>268</v>
       </c>
       <c r="F226" t="n">
-        <v>21806</v>
+        <v>21805</v>
       </c>
       <c r="G226" t="n">
         <v>7975.41</v>
@@ -6790,7 +6779,7 @@
         <v>415</v>
       </c>
       <c r="F227" t="n">
-        <v>102533</v>
+        <v>102531</v>
       </c>
       <c r="G227" t="n">
         <v>8005.940000000001</v>
@@ -7381,10 +7370,10 @@
         <v>61837</v>
       </c>
       <c r="G248" t="n">
-        <v>26673.72</v>
+        <v>20108.47</v>
       </c>
       <c r="H248" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="249">
@@ -7468,7 +7457,7 @@
         <v>40588.92</v>
       </c>
       <c r="H251" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="252">
@@ -7605,10 +7594,10 @@
         <v>1927</v>
       </c>
       <c r="G256" t="n">
-        <v>13672.88</v>
+        <v>12317.8</v>
       </c>
       <c r="H256" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="257">
@@ -7829,10 +7818,10 @@
         <v>42258</v>
       </c>
       <c r="G264" t="n">
-        <v>23344.14</v>
+        <v>27080.58</v>
       </c>
       <c r="H264" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="265">
@@ -7848,13 +7837,13 @@
         </is>
       </c>
       <c r="D265" t="n">
-        <v>2820.49</v>
+        <v>2816</v>
       </c>
       <c r="E265" t="n">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="F265" t="n">
-        <v>52684</v>
+        <v>52683</v>
       </c>
       <c r="G265" t="n">
         <v>17878.82</v>
@@ -7885,10 +7874,10 @@
         <v>15397</v>
       </c>
       <c r="G266" t="n">
-        <v>11262.7</v>
+        <v>5842.38</v>
       </c>
       <c r="H266" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="267">
@@ -7969,10 +7958,10 @@
         <v>11181</v>
       </c>
       <c r="G269" t="n">
-        <v>4606.78</v>
+        <v>5891.53</v>
       </c>
       <c r="H269" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="270">
@@ -8277,10 +8266,10 @@
         <v>35884</v>
       </c>
       <c r="G280" t="n">
-        <v>8150.85</v>
+        <v>9226.27</v>
       </c>
       <c r="H280" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="281">
@@ -8641,10 +8630,10 @@
         <v>3038</v>
       </c>
       <c r="G293" t="n">
-        <v>4235.59</v>
+        <v>2880.51</v>
       </c>
       <c r="H293" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="294">
@@ -8809,10 +8798,10 @@
         <v>7388</v>
       </c>
       <c r="G299" t="n">
-        <v>14065.24</v>
+        <v>12710.16</v>
       </c>
       <c r="H299" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="300">
@@ -8837,10 +8826,10 @@
         <v>4959</v>
       </c>
       <c r="G300" t="n">
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="H300" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="301">
@@ -8893,10 +8882,10 @@
         <v>14796</v>
       </c>
       <c r="G302" t="n">
-        <v>21043.22</v>
+        <v>19688.14</v>
       </c>
       <c r="H302" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="303">
@@ -8921,7 +8910,7 @@
         <v>76532</v>
       </c>
       <c r="G303" t="n">
-        <v>50231.36</v>
+        <v>47944.07</v>
       </c>
       <c r="H303" t="n">
         <v>10</v>
@@ -8968,13 +8957,13 @@
         </is>
       </c>
       <c r="D305" t="n">
-        <v>2298.55</v>
+        <v>2272.18</v>
       </c>
       <c r="E305" t="n">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F305" t="n">
-        <v>34797</v>
+        <v>34795</v>
       </c>
       <c r="G305" t="n">
         <v>19283.08</v>
@@ -9002,7 +8991,7 @@
         <v>216</v>
       </c>
       <c r="F306" t="n">
-        <v>43481</v>
+        <v>43456</v>
       </c>
       <c r="G306" t="n">
         <v>11518.62</v>
@@ -9148,7 +9137,7 @@
         <v>2033.05</v>
       </c>
       <c r="H311" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="312">
@@ -9310,7 +9299,7 @@
         <v>107</v>
       </c>
       <c r="F317" t="n">
-        <v>17594</v>
+        <v>17593</v>
       </c>
       <c r="G317" t="n">
         <v>2324.58</v>
@@ -9394,7 +9383,7 @@
         <v>312</v>
       </c>
       <c r="F320" t="n">
-        <v>44231</v>
+        <v>44226</v>
       </c>
       <c r="G320" t="n">
         <v>15959.35</v>
@@ -9418,42 +9407,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
@@ -10206,7 +10195,7 @@
         <v>708</v>
       </c>
       <c r="F28" t="n">
-        <v>133945</v>
+        <v>133936</v>
       </c>
       <c r="G28" t="n">
         <v>20760.17</v>
@@ -10433,10 +10422,10 @@
         <v>62895</v>
       </c>
       <c r="G36" t="n">
-        <v>21028.8</v>
+        <v>17513.55</v>
       </c>
       <c r="H36" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37">
@@ -10536,19 +10525,19 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>5100.52</v>
+        <v>5099.05</v>
       </c>
       <c r="E40" t="n">
-        <v>3086</v>
+        <v>3084</v>
       </c>
       <c r="F40" t="n">
-        <v>670537</v>
+        <v>670532</v>
       </c>
       <c r="G40" t="n">
-        <v>17240.67</v>
+        <v>15929.67</v>
       </c>
       <c r="H40" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -10829,6 +10818,2080 @@
       </c>
       <c r="H50" t="n">
         <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I62"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Portfolio name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Campaign Name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Advertised ASIN</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Impressions</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Clicks</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>14 Day Total Sales (₹)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>14 Day Total Units (#)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Audio Array-B0CKHVHVQ1-AM W45 Wireless-SBV-KT-Phrase</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>B0CKHVHVQ1</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>73469</v>
+      </c>
+      <c r="E2" t="n">
+        <v>184</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2978.57</v>
+      </c>
+      <c r="G2" t="n">
+        <v>4185.59</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Audio Array-B0CKHVHVQ1-AM W45 Wireless-SBV-PT</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>B0CKHVHVQ1</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>19944</v>
+      </c>
+      <c r="E3" t="n">
+        <v>144</v>
+      </c>
+      <c r="F3" t="n">
+        <v>687.7138926088076</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4575.42</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Audio Array-B0CKHVHVQ1-AM W45 Wireless-SBV-PT</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>B0G39ZHDYP</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>4429</v>
+      </c>
+      <c r="E4" t="n">
+        <v>32</v>
+      </c>
+      <c r="F4" t="n">
+        <v>152.7261073911924</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1016.1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>B0B4DPX2J2</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>376</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>18.57785714285714</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>B0B4DS678Q</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>376</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>18.57785714285714</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>B0B4G19R58</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>7253</v>
+      </c>
+      <c r="E7" t="n">
+        <v>87</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1760.541856558983</v>
+      </c>
+      <c r="G7" t="n">
+        <v>12929.22857113566</v>
+      </c>
+      <c r="H7" t="n">
+        <v>5</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>B0B4JRQP22</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>376</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="n">
+        <v>18.57785714285714</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>B0B4K87PR4</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>9357</v>
+      </c>
+      <c r="E9" t="n">
+        <v>51</v>
+      </c>
+      <c r="F9" t="n">
+        <v>423.9692723464653</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2990.679999999999</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>B0B4KC7VBM</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>376</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" t="n">
+        <v>18.57785714285714</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>B0BLJVJ2GN</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>376</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" t="n">
+        <v>18.57785714285714</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>B0BLK8DNPD</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>376</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" t="n">
+        <v>18.57785714285714</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>B0BLKB55BM</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>376</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" t="n">
+        <v>18.57785714285714</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>B0BPLWW72Y</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>3586</v>
+      </c>
+      <c r="E14" t="n">
+        <v>19</v>
+      </c>
+      <c r="F14" t="n">
+        <v>161.8580814905548</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1194.07</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>B0BPLZ5CGV</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>3265</v>
+      </c>
+      <c r="E15" t="n">
+        <v>38</v>
+      </c>
+      <c r="F15" t="n">
+        <v>750.2793802910481</v>
+      </c>
+      <c r="G15" t="n">
+        <v>5430.844863500047</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>B0C4YTNJG7</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>376</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" t="n">
+        <v>18.57785714285714</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>B0C539RBGL</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>376</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" t="n">
+        <v>18.57785714285714</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>B0CF5R3V95</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>376</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" t="n">
+        <v>18.57785714285714</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>B0CF5RRTDJ</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>376</v>
+      </c>
+      <c r="E19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" t="n">
+        <v>18.57785714285714</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>B0CF5TCQKL</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>376</v>
+      </c>
+      <c r="E20" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" t="n">
+        <v>18.57785714285714</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>B0CH4RT4P8</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>376</v>
+      </c>
+      <c r="E21" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" t="n">
+        <v>18.57785714285714</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>B0CKHVHVQ1</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>80571</v>
+      </c>
+      <c r="E22" t="n">
+        <v>433</v>
+      </c>
+      <c r="F22" t="n">
+        <v>3638.377213044691</v>
+      </c>
+      <c r="G22" t="n">
+        <v>26704.21999999999</v>
+      </c>
+      <c r="H22" t="n">
+        <v>7</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>B0CM6NTWBP</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>376</v>
+      </c>
+      <c r="E23" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" t="n">
+        <v>18.57785714285714</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>B0CM6NVLT9</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>962</v>
+      </c>
+      <c r="E24" t="n">
+        <v>12</v>
+      </c>
+      <c r="F24" t="n">
+        <v>243.7979566967016</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1809.520465614685</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>B0D3M1B4Z8</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>2482</v>
+      </c>
+      <c r="E25" t="n">
+        <v>29</v>
+      </c>
+      <c r="F25" t="n">
+        <v>552.0680504118114</v>
+      </c>
+      <c r="G25" t="n">
+        <v>3959.678071157382</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>B0DFMLS8JG</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>376</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" t="n">
+        <v>18.57785714285714</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>B0DFMMTWLY</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>376</v>
+      </c>
+      <c r="E27" t="n">
+        <v>3</v>
+      </c>
+      <c r="F27" t="n">
+        <v>18.57785714285714</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>B0DFMNGFTD</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>376</v>
+      </c>
+      <c r="E28" t="n">
+        <v>3</v>
+      </c>
+      <c r="F28" t="n">
+        <v>18.57785714285714</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>B0DT6T6N6B</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>376</v>
+      </c>
+      <c r="E29" t="n">
+        <v>3</v>
+      </c>
+      <c r="F29" t="n">
+        <v>18.57785714285714</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>B0FF9R3GKK</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>2091</v>
+      </c>
+      <c r="E30" t="n">
+        <v>24</v>
+      </c>
+      <c r="F30" t="n">
+        <v>452.9641846128835</v>
+      </c>
+      <c r="G30" t="n">
+        <v>3224.108028592225</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>B0G2C2RCXN</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>376</v>
+      </c>
+      <c r="E31" t="n">
+        <v>3</v>
+      </c>
+      <c r="F31" t="n">
+        <v>18.57785714285714</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>B0G3Q517Y2</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>376</v>
+      </c>
+      <c r="E32" t="n">
+        <v>3</v>
+      </c>
+      <c r="F32" t="n">
+        <v>18.57785714285714</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>B0G3Q59X8C</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>376</v>
+      </c>
+      <c r="E33" t="n">
+        <v>3</v>
+      </c>
+      <c r="F33" t="n">
+        <v>18.57785714285714</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>B0G4DNF8RZ</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>376</v>
+      </c>
+      <c r="E34" t="n">
+        <v>3</v>
+      </c>
+      <c r="F34" t="n">
+        <v>18.57785714285714</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>B0H3LHF2WW</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>6360</v>
+      </c>
+      <c r="E35" t="n">
+        <v>34</v>
+      </c>
+      <c r="F35" t="n">
+        <v>287.0711474040023</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2117.8</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Audio Array_B0DXFPM4N2_Studio Monitor_SB Video</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>B0DXFPM4N2</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>24618</v>
+      </c>
+      <c r="E36" t="n">
+        <v>198</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1176.09</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Audio Array_SB_Branded_KT</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>B0B4DPX2J2</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>71</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" t="n">
+        <v>24.716</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Audio Array_SB_Branded_KT</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>B0BPLZ5CGV</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>71</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" t="n">
+        <v>24.716</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Audio Array_SB_Branded_KT</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>B0FG88HVQ8</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>71</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" t="n">
+        <v>24.716</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Audio Array_SB_Branded_KT</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>B0G3B152FR</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>71</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" t="n">
+        <v>24.716</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Audio Array_SB_Branded_KT</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>B0G53H49BS</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>71</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" t="n">
+        <v>24.716</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Audio Array_Studio Headphones_SB_KT_Phrase</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>B0FG88HVQ8</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>16605</v>
+      </c>
+      <c r="E42" t="n">
+        <v>30</v>
+      </c>
+      <c r="F42" t="n">
+        <v>283.8604975736107</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1600.85</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Audio Array_Studio Headphones_SB_KT_Phrase</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>B0FQBTRM28</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>17713</v>
+      </c>
+      <c r="E43" t="n">
+        <v>32</v>
+      </c>
+      <c r="F43" t="n">
+        <v>302.7945787997782</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1707.63</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Audio Array_Studio Headphones_SB_KT_Phrase</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>B0FQBXS6Y2</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>13177</v>
+      </c>
+      <c r="E44" t="n">
+        <v>24</v>
+      </c>
+      <c r="F44" t="n">
+        <v>225.2549236266113</v>
+      </c>
+      <c r="G44" t="n">
+        <v>1270.34</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>AudioArray - Condenser Mic - SB - KT</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>B0B4DPX2J2</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>9101</v>
+      </c>
+      <c r="E45" t="n">
+        <v>57</v>
+      </c>
+      <c r="F45" t="n">
+        <v>433.53</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>AudioArray - Conference Mic - SB - AD</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>B0B4KC7VBM</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>3232</v>
+      </c>
+      <c r="E46" t="n">
+        <v>21</v>
+      </c>
+      <c r="F46" t="n">
+        <v>216.47</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1961.86</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>AudioArray - Podcast Mic  SB - KT</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>B0B4DPX2J2</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>1629</v>
+      </c>
+      <c r="E47" t="n">
+        <v>21</v>
+      </c>
+      <c r="F47" t="n">
+        <v>291.342956860282</v>
+      </c>
+      <c r="G47" t="n">
+        <v>2117.8</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>AudioArray - Podcast Mic  SB - KT</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>B0FJS57732</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>1825</v>
+      </c>
+      <c r="E48" t="n">
+        <v>23</v>
+      </c>
+      <c r="F48" t="n">
+        <v>326.317043139718</v>
+      </c>
+      <c r="G48" t="n">
+        <v>2372.03</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>AudioArray - Sound Bar - SB - KT</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>B0FFB6YJM1</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>9067</v>
+      </c>
+      <c r="E49" t="n">
+        <v>93</v>
+      </c>
+      <c r="F49" t="n">
+        <v>613.9</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>AudioArray - Voice Amplifier - SB - KT</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>B0G3B152FR</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>12875</v>
+      </c>
+      <c r="E50" t="n">
+        <v>85</v>
+      </c>
+      <c r="F50" t="n">
+        <v>496.3</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>AudioArray_Audio Mixers_SB_Collection</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>B0G53H49BS</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>495</v>
+      </c>
+      <c r="E51" t="n">
+        <v>6</v>
+      </c>
+      <c r="F51" t="n">
+        <v>50.464</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>AudioArray_Audio Mixers_SB_Collection</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>B0G53M9258</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>495</v>
+      </c>
+      <c r="E52" t="n">
+        <v>6</v>
+      </c>
+      <c r="F52" t="n">
+        <v>50.464</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>AudioArray_Audio Mixers_SB_Collection</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>B0GCP1J2HC</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>495</v>
+      </c>
+      <c r="E53" t="n">
+        <v>6</v>
+      </c>
+      <c r="F53" t="n">
+        <v>50.464</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>AudioArray_Audio Mixers_SB_Collection</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>B0GXP97CZG</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>495</v>
+      </c>
+      <c r="E54" t="n">
+        <v>6</v>
+      </c>
+      <c r="F54" t="n">
+        <v>50.464</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>AudioArray_Audio Mixers_SB_Collection</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>B0GXPBHDRF</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>495</v>
+      </c>
+      <c r="E55" t="n">
+        <v>6</v>
+      </c>
+      <c r="F55" t="n">
+        <v>50.464</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>AudioArray_B0BPLZ5CGV_Audio Interface AI04_SB_ KT</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>B0BPLZ5CGV</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>15864</v>
+      </c>
+      <c r="E56" t="n">
+        <v>189</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1378.17</v>
+      </c>
+      <c r="G56" t="n">
+        <v>23555.08</v>
+      </c>
+      <c r="H56" t="n">
+        <v>5</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>AudioArray_B0DXFPM4N2_Studio Monitor AM-S1_SB_KT</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>B0DXFPM4N2</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>9166</v>
+      </c>
+      <c r="E57" t="n">
+        <v>116</v>
+      </c>
+      <c r="F57" t="n">
+        <v>549.8199999999999</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>AudioArray_B0G3Q59X8C_Wireless Mic_SB_KT</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>B0G3Q59X8C</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>4042</v>
+      </c>
+      <c r="E58" t="n">
+        <v>55</v>
+      </c>
+      <c r="F58" t="n">
+        <v>390.39</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>AudioArray_B0G53H49BS_Audio Mixer_SB_KT</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>B0G53H49BS</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>11057</v>
+      </c>
+      <c r="E59" t="n">
+        <v>114</v>
+      </c>
+      <c r="F59" t="n">
+        <v>587.78</v>
+      </c>
+      <c r="G59" t="n">
+        <v>2234.75</v>
+      </c>
+      <c r="H59" t="n">
+        <v>1</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>AudioArray_B0GKPXQ8G3_Wireless Mic_SB_KT</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>B0GKPXQ8G3</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>6561</v>
+      </c>
+      <c r="E60" t="n">
+        <v>48</v>
+      </c>
+      <c r="F60" t="n">
+        <v>334.56</v>
+      </c>
+      <c r="G60" t="n">
+        <v>2541.53</v>
+      </c>
+      <c r="H60" t="n">
+        <v>1</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>AudioArray_B0GN97RFPR_Studio Monitor_SB_KT</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>B0GN97RFPR</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>20102</v>
+      </c>
+      <c r="E61" t="n">
+        <v>197</v>
+      </c>
+      <c r="F61" t="n">
+        <v>1024.96</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>AudioArray_UHF Wireless Microphone_SB_Collection</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>B0B4G59Y8W</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>4421</v>
+      </c>
+      <c r="E62" t="n">
+        <v>22</v>
+      </c>
+      <c r="F62" t="n">
+        <v>421.38</v>
+      </c>
+      <c r="G62" t="n">
+        <v>1609.32</v>
+      </c>
+      <c r="H62" t="n">
+        <v>1</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
       </c>
     </row>
   </sheetData>
